--- a/artfynd/A 49108-2024 artfynd.xlsx
+++ b/artfynd/A 49108-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>120803755</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49108-2024 artfynd.xlsx
+++ b/artfynd/A 49108-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>120803755</v>
       </c>
       <c r="B3" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
